--- a/Data/g13.1a.xlsx
+++ b/Data/g13.1a.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Distrito Federal</t>
+          <t>Santa Catarina</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -468,11 +468,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55.79</v>
+        <v>56.18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -493,11 +493,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.67</v>
+        <v>56.14</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -508,7 +508,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Santa Catarina</t>
+          <t>Distrito Federal</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -518,11 +518,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>55.62</v>
+        <v>55.68</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -533,7 +533,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Rio Grande do Sul</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -543,11 +543,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>54.89</v>
+        <v>54.88</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -558,7 +558,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Rio Grande do Sul</t>
+          <t>Mato Grosso</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -568,11 +568,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>54.54</v>
+        <v>54.52</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mato Grosso</t>
+          <t>Paraná</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -593,11 +593,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>54.28</v>
+        <v>54.35</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -618,15 +618,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>44.83</v>
+        <v>45.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18º</t>
+          <t>19º</t>
         </is>
       </c>
     </row>
@@ -643,11 +643,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>51.04</v>
+        <v>51.01</v>
       </c>
       <c r="E9" t="inlineStr"/>
     </row>
@@ -664,11 +664,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>01/04/2025</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>44.07</v>
+        <v>43.98</v>
       </c>
       <c r="E10" t="inlineStr"/>
     </row>
